--- a/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
+++ b/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
@@ -18,17 +18,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Item Name</t>
+          <t>Item Description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>FOB Cost</t>
+          <t>FOB</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Freight/Unit</t>
+          <t>Ocean/Unit</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -38,22 +38,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Landed Cost</t>
+          <t>Landed</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Retail Price</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Gross Margin %</t>
+          <t>Margin %</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Reorder Point</t>
+          <t>Reorder Level</t>
         </is>
       </c>
     </row>
@@ -65,7 +65,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stainless Pour-Over Kettle 1.2L</t>
+          <t>Precision Kettle</t>
         </is>
       </c>
       <c r="C2">
@@ -100,7 +100,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Burr Hand Grinder Aluminum</t>
+          <t>Burr Grinder</t>
         </is>
       </c>
       <c r="C3">
@@ -135,7 +135,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Digital Espresso Scale</t>
+          <t>Digital Scale</t>
         </is>
       </c>
       <c r="C4">
@@ -170,7 +170,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Double-Wall Glass Mug Set (2pk)</t>
+          <t>Glass Mugs 2pk</t>
         </is>
       </c>
       <c r="C5">

--- a/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
+++ b/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
@@ -1,202 +1,681 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Margin_Calculator_v1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin_Calculator_v1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
+  </fonts>
+  <fills count="5">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Item Description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>FOB</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ocean/Unit</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Duty/Unit</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Landed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Margin %</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Reorder Level</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>KC-101</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Precision Kettle</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="C2" s="4" t="n">
         <v>8.4</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4" t="n">
         <v>10.37</v>
       </c>
-      <c r="G2">
-        <v>34.0</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>69.5%</t>
         </is>
       </c>
-      <c r="I2">
+      <c r="I2" s="4" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>KC-102</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Burr Grinder</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" s="7" t="n">
         <v>14.2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="7" t="n">
         <v>0.51</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="7" t="n">
         <v>0.53</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7" t="n">
         <v>15.24</v>
       </c>
-      <c r="G3">
-        <v>58.0</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>73.7%</t>
         </is>
       </c>
-      <c r="I3">
+      <c r="I3" s="7" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>KC-103</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Digital Scale</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="C4" s="4" t="n">
         <v>6.15</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4" t="n">
         <v>6.69</v>
       </c>
-      <c r="G4">
-        <v>29.0</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>76.9%</t>
         </is>
       </c>
-      <c r="I4">
+      <c r="I4" s="4" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>KC-104</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Glass Mugs 2pk</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="C5" s="7" t="n">
         <v>3.8</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7" t="n">
         <v>0.63</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7" t="n">
         <v>4.66</v>
       </c>
-      <c r="G5">
-        <v>24.0</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>80.6%</t>
         </is>
       </c>
-      <c r="I5">
+      <c r="I5" s="7" t="n">
         <v>300</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
+++ b/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -86,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,7 +100,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,7 +115,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,205 +489,1343 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SKU Code</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Description</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>FOB</t>
+          <t>FOB Ningbo USD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ocean/Unit</t>
+          <t>Ocean Freight / Unit</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Duty/Unit</t>
+          <t>Customs Tariff (24.5%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Landed</t>
+          <t>Port Drayage / Unit</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Total Landed Cost</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Amazon FBA Fee</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Reorder Level</t>
+          <t>FBA Referral (15%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Wholesale Price (50% Margin)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Retail MSRP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KC-101</t>
+          <t>PHG-WD-01</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Precision Kettle</t>
+          <t>Acacia Cutting Board (M)</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>10.37</v>
+        <v>4.25</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.22</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>69.5%</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>180</v>
+        <v>6.09</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>51.3</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>KC-102</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Burr Grinder</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>73.7%</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>120</v>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>PHG-WD-02</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Acacia Cutting Board (L)</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>50.8</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KC-103</t>
+          <t>PHG-WD-03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Digital Scale</t>
+          <t>Teak Butcher Block</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E4" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>PHG-WD-04</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Walnut Serving Platter</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PHG-WD-05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Teak Salad Bowl Set</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CR-01</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic Coffee Mug (12oz)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PHG-CR-02</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Ceramic Tumbler (16oz)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CR-03</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic Dinner Plate (10.5in)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PHG-CR-04</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Ceramic Salad Plate (8.5in)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CR-05</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic Pasta Bowl (9in)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>PHG-GL-01</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Ribbed Rocks Glass (10oz)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>PHG-GL-02</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Ribbed Highball Glass (14oz)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>0.28</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E13" s="11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PHG-GL-03</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Glass Cocktail Decanter</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>PHG-TX-01</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>French Linen Towel (2pk)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PHG-TX-02</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Linen Table Runner</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>PHG-TX-03</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Linen Napkin Set (4pk)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PHG-MT-01</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Brass Measuring Cups Set</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>PHG-MT-02</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Vintage Brass Shaker</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PHG-MT-03</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Japanese Brass Jigger</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>PHG-MT-04</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Cast Iron Skillet (10in)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PHG-MT-05</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cast Iron Skillet (12in)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CD-01</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Soy Candle in Ceramic (8oz)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PHG-CD-02</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Soy Candle in Brass (12oz)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CD-03</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Reed Diffuser (200ml)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PHG-ST-01</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Hyacinth Storage Basket (M)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>PHG-ST-02</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Hyacinth Storage Basket (L)</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J27" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>76.9%</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>KC-104</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Glass Mugs 2pk</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="G5" s="7" t="n">
+      <c r="K27" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PHG-BA-01</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Waffle Bath Towel</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>80.6%</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>300</v>
+      <c r="K28" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>PHG-BA-02</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Waffle Hand Towel (2pk)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PHG-BA-03</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Stone Bath Mat</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>PHG-WD-06</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Teak Coaster Set (4pk)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>63.3</v>
       </c>
     </row>
   </sheetData>

--- a/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
+++ b/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin_Calculator_v1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Trail &amp; Documentation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,6 +124,9 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,7 +494,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
@@ -1831,4 +1835,4648 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Hash</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Parameter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed SLA Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Clearance Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sign-Off Authority</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 1</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:540deb7669156511c863dbdb</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 2</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f7ded495162de72a67ea4854</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:3603c066f7b4ae9f054e5111</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 4</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:c969b391f9880820a54ce678</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 5</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:6e71561121d19b8411a621a1</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 6</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f7b801a9f3202419f7f4e492</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 7</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:62c62c7a9f43b42884529245</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 8</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:dbc2e9293e6bf2bebbde2d60</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 9</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:30fa42537bfb0437c7d43e37</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 10</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:cc8941aee2b2a57b46d8edae</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 11</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:c4e22e088306f3cd8770f119</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 12</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f55501bcdbd7fafd92c81471</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 13</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:4cfd0482bc4748af31620541</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 14</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:74e0bb3f9db2a3792faadd00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 15</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:a2813dfe324b68fdf80130e9</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 16</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:da87bc08a2c815ea4dc1d48a</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 17</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:a8f5da4cf51f88e603619b80</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 18</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:c21d335aaec1b52645d3a0fe</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 19</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:6226f132a709b57fabf39378</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 20</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f9c362babff802eb5fdcffac</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 21</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:c83f61074c0f6e432b45ece0</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 22</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:3861a893cb80e9590d73222c</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 23</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:fe2ddacde461256b5f08d27c</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 24</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:7906cc548202d1de58a3f737</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 25</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:73c8c85772c3221ccff8c47e</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 26</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:d1317d3978037deb08339516</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 27</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:d43c6575b0ca1b68f50e33d4</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 28</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:8520908b382e44b134e4f0eb</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 29</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:d2566c955ed7f9bc26364e60</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 30</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:b4f0e1378d635abca34eda22</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 31</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:78a118d65b25b93080f3b36f</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 32</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:e64ac7dc72d65d553c4cf25b</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 33</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:738de8a6e48106eb66e6f369</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 34</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:ed2cb0a3fb6e1548cd864f5d</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 35</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:ef0a284ba0d6384307c01481</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 36</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:bf112b05b70f8b03185be9ae</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 37</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:066dfee11d424a9f6652c67c</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 38</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:de55bfd4bc6fcd3f71abf340</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 39</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:4ff7804472b80e24af920ee2</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 40</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:5365440c9322e125b6ce76a8</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 41</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:d86edb3e5abf4a4c69b8d8a9</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 42</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:b45db66614f1c2231f3a7ef9</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 43</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:bc2d8644a130a9886a876877</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 44</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:4fc5f10491b1a050e770c3ba</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 45</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f9868fe5f8094b7c04ab2ce8</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 46</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:44a389c09415a366c84dbccf</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 47</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:552719fb71cb09b1fc870977</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 48</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:e1f155c4095487c58f71c703</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 49</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:147fc2ced54f682ccca1b558</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 50</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:57cb0c402fb86a86035e226c</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 51</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:8a5605f39e6d4aafc493881b</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 52</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:69f0f97019e43cead9a93c35</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 53</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:ddea4861aa07f1fd06d7eadb</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 54</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:2022ef4c0c663f4c0a0f82b2</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 55</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:7d07873b0b0884a12d22b25c</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 56</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:bd6871a57c26803de031a923</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 57</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:2948ed50e398f60c5fd03b2d</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 58</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:59d2740a341a8effe4ed00f1</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 59</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:e4d7119b6591198b6b498b0e</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 60</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:074f9f0effc80d638a5a5b64</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 61</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:3afc4ed9e9183dff8d3bddeb</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 62</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:e4b3fb48a503f555ff0a1d33</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 63</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:dddb97eb91652f5b642ece93</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 64</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:2e621c2287adb2a3054cea15</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 65</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:7a392e95fbd74f2bd83af1c1</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 66</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:1b50ca93333d4867d6b44d46</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 67</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:19e096cd2d9dae1b4f3aaef7</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 68</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:55c9d6aab4db2b2f22b713f5</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 69</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:ee4dfa6cb84a9fd7fc3a2077</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 70</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:648298764a2af70be940f310</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 71</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:da11bc3f2e073abfe7ab883c</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 72</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:520860677a911803b2676921</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 73</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:6a2002087c8b2ed5922516f6</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 74</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:d6dcdb3ce633fbbbe4b561b1</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 75</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:d915b5e1e680ebc506fcb9e4</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 76</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:54243efb0a4c3445cbd12e5c</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 77</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:cf35c2c66616ed0cdb1a2df3</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 78</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:48230e437e315f5bfdab0dd4</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 79</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:51a775a26ce8e3d48f0569aa</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 80</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:9cc13dba8add7bec0e1e63aa</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 81</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:fe1f8f5b50b7a6337944ee12</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 82</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:4f0a92b728f52f9055e67914</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 83</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:1c91a2fbd199c5b8bb40bcaa</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 84</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:6597be44831de74ef2f48c93</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 85</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:ec81d72c1ee8f9639f1da0c7</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 86</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f5764ac3a01ae92dc7d800b6</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 87</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:5cc42a632a0701c16babaa14</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 88</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:085c0ef9db880034d4c8a8aa</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 89</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:ae455e10948a37e8d9ec49bd</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 90</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:9e3786c74bbd49edddbc2982</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 91</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:a21857b532115b1c42230399</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 92</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:258788af5762110177df1c71</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 93</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f18e21487fd6a108663431be</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 94</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:1162707c9acde069cdd3bdc3</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 95</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:0a568ec5c427b062bb6100f1</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 96</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:baf1aff3f235e6cabe347606</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 97</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:23bff035e23288c977168419</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 98</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:4954aabb066fc0ec6ddcd1fb</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 99</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:418979642d88c8ef8f773d9f</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 100</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:5cc38c8c840947984ff65921</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 101</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:e63573f39c8c5de853278444</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 102</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:5be6048a7e97fee8eff18339</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 103</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:a77af74c3be52e4b035b3b34</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 104</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:e184eb8fc6a75330a13cfffd</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 105</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:659d41aa2a9e1ddfe7aef3bf</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 106</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:a63c23969482903391d08f93</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 107</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:3f9a018e33ba0d3c12b9b3cd</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 108</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:f8b643183d4554e185e0ffa0</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>AUD-REC-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 109</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>SHA256:06e1f268c255b106f5140901</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
+++ b/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
@@ -17,10 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -90,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,13 +98,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,13 +107,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -493,1343 +478,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKU Code</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Item Description</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>FOB Ningbo USD</t>
+          <t>FOB</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ocean Freight / Unit</t>
+          <t>Ocean/Unit</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Customs Tariff (24.5%)</t>
+          <t>Duty/Unit</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Port Drayage / Unit</t>
+          <t>Landed</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Total Landed Cost</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Amazon FBA Fee</t>
+          <t>Margin %</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>FBA Referral (15%)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Wholesale Price (50% Margin)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Retail MSRP</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
+          <t>Reorder Level</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PHG-WD-01</t>
+          <t>KC-101</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Acacia Cutting Board (M)</t>
+          <t>Precision Kettle</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0.22</v>
+        <v>8.4</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>10.37</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L2" s="6" t="n">
-        <v>51.3</v>
+        <v>34</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>69.5%</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>PHG-WD-02</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Acacia Cutting Board (L)</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>50.8</v>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>KC-102</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Burr Grinder</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PHG-WD-03</t>
+          <t>KC-103</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Teak Butcher Block</t>
+          <t>Digital Scale</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.35</v>
+        <v>6.15</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6.69</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>49.1</v>
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>PHG-WD-04</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Walnut Serving Platter</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>50.9</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>PHG-WD-05</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Teak Salad Bowl Set</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>15.59</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>51.3</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>PHG-CR-01</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Ceramic Coffee Mug (12oz)</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>57.4</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PHG-CR-02</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Ceramic Tumbler (16oz)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>PHG-CR-03</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Ceramic Dinner Plate (10.5in)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>PHG-CR-04</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Ceramic Salad Plate (8.5in)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K10" s="5" t="n">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>KC-104</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Glass Mugs 2pk</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="L10" s="6" t="n">
-        <v>58.3</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>PHG-CR-05</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Ceramic Pasta Bowl (9in)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>PHG-GL-01</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Ribbed Rocks Glass (10oz)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>PHG-GL-02</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Ribbed Highball Glass (14oz)</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>60.8</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>PHG-GL-03</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Glass Cocktail Decanter</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>57.1</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>PHG-TX-01</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>French Linen Towel (2pk)</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>PHG-TX-02</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Linen Table Runner</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>56.8</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>PHG-TX-03</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Linen Napkin Set (4pk)</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="K17" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>58.6</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>PHG-MT-01</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Brass Measuring Cups Set</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>58.1</v>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>PHG-MT-02</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Vintage Brass Shaker</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="L19" s="11" t="n">
-        <v>55.6</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>PHG-MT-03</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Japanese Brass Jigger</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>64.7</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>PHG-MT-04</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Cast Iron Skillet (10in)</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="K21" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="L21" s="11" t="n">
-        <v>53.2</v>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>PHG-MT-05</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Cast Iron Skillet (12in)</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>51.8</v>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>PHG-CD-01</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Soy Candle in Ceramic (8oz)</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>PHG-CD-02</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Soy Candle in Brass (12oz)</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>60.3</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>PHG-CD-03</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Reed Diffuser (200ml)</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K25" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="L25" s="11" t="n">
-        <v>56.6</v>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>PHG-ST-01</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Hyacinth Storage Basket (M)</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>60.6</v>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>PHG-ST-02</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Hyacinth Storage Basket (L)</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="K27" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="L27" s="11" t="n">
-        <v>57.7</v>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>PHG-BA-01</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Waffle Bath Towel</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>PHG-BA-02</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Waffle Hand Towel (2pk)</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K29" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="L29" s="11" t="n">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>PHG-BA-03</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Stone Bath Mat</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>58.1</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>PHG-WD-06</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Teak Coaster Set (4pk)</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K31" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L31" s="11" t="n">
-        <v>63.3</v>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>80.6%</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -1899,4578 +746,4578 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0001</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 1</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>SHA256:540deb7669156511c863dbdb</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0002</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 2</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>SHA256:f7ded495162de72a67ea4854</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0003</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 3</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>SHA256:3603c066f7b4ae9f054e5111</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0004</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 4</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>SHA256:c969b391f9880820a54ce678</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0005</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 5</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SHA256:6e71561121d19b8411a621a1</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0006</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 6</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>SHA256:f7b801a9f3202419f7f4e492</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0007</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 7</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>SHA256:62c62c7a9f43b42884529245</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0008</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 8</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>SHA256:dbc2e9293e6bf2bebbde2d60</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0009</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 9</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>SHA256:30fa42537bfb0437c7d43e37</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0010</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 10</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>SHA256:cc8941aee2b2a57b46d8edae</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0011</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 11</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>SHA256:c4e22e088306f3cd8770f119</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0012</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 12</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>SHA256:f55501bcdbd7fafd92c81471</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0013</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 13</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>SHA256:4cfd0482bc4748af31620541</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0014</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 14</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>SHA256:74e0bb3f9db2a3792faadd00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0015</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 15</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>SHA256:a2813dfe324b68fdf80130e9</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0016</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 16</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>SHA256:da87bc08a2c815ea4dc1d48a</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0017</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 17</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>SHA256:a8f5da4cf51f88e603619b80</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0018</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 18</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>SHA256:c21d335aaec1b52645d3a0fe</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0019</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 19</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>SHA256:6226f132a709b57fabf39378</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0020</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 20</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>SHA256:f9c362babff802eb5fdcffac</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0021</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 21</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>SHA256:c83f61074c0f6e432b45ece0</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0022</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 22</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>SHA256:3861a893cb80e9590d73222c</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0023</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 23</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>SHA256:fe2ddacde461256b5f08d27c</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0024</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 24</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>SHA256:7906cc548202d1de58a3f737</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0025</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 25</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>SHA256:73c8c85772c3221ccff8c47e</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0026</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 26</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>SHA256:d1317d3978037deb08339516</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0027</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 27</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>SHA256:d43c6575b0ca1b68f50e33d4</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0028</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 28</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>SHA256:8520908b382e44b134e4f0eb</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0029</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 29</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>SHA256:d2566c955ed7f9bc26364e60</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0030</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 30</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>SHA256:b4f0e1378d635abca34eda22</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0031</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 31</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>SHA256:78a118d65b25b93080f3b36f</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0032</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 32</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>SHA256:e64ac7dc72d65d553c4cf25b</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0033</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 33</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>SHA256:738de8a6e48106eb66e6f369</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0034</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 34</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>SHA256:ed2cb0a3fb6e1548cd864f5d</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0035</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 35</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>SHA256:ef0a284ba0d6384307c01481</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0036</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 36</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>SHA256:bf112b05b70f8b03185be9ae</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0037</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 37</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>SHA256:066dfee11d424a9f6652c67c</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0038</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 38</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>SHA256:de55bfd4bc6fcd3f71abf340</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0039</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 39</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>SHA256:4ff7804472b80e24af920ee2</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0040</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 40</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>SHA256:5365440c9322e125b6ce76a8</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0041</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 41</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>SHA256:d86edb3e5abf4a4c69b8d8a9</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0042</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 42</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>SHA256:b45db66614f1c2231f3a7ef9</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0043</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 43</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>SHA256:bc2d8644a130a9886a876877</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0044</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 44</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>SHA256:4fc5f10491b1a050e770c3ba</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0045</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 45</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>SHA256:f9868fe5f8094b7c04ab2ce8</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0046</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 46</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>SHA256:44a389c09415a366c84dbccf</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0047</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 47</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>SHA256:552719fb71cb09b1fc870977</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0048</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 48</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>SHA256:e1f155c4095487c58f71c703</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0049</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 49</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>SHA256:147fc2ced54f682ccca1b558</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0050</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 50</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>SHA256:57cb0c402fb86a86035e226c</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0051</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 51</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHA256:8a5605f39e6d4aafc493881b</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0052</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 52</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>SHA256:69f0f97019e43cead9a93c35</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0053</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 53</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>SHA256:ddea4861aa07f1fd06d7eadb</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0054</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 54</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>SHA256:2022ef4c0c663f4c0a0f82b2</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0055</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 55</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>SHA256:7d07873b0b0884a12d22b25c</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0056</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 56</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>SHA256:bd6871a57c26803de031a923</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0057</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 57</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>SHA256:2948ed50e398f60c5fd03b2d</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0058</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 58</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>SHA256:59d2740a341a8effe4ed00f1</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0059</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 59</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>SHA256:e4d7119b6591198b6b498b0e</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0060</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 60</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>SHA256:074f9f0effc80d638a5a5b64</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0061</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 61</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>SHA256:3afc4ed9e9183dff8d3bddeb</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0062</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 62</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>SHA256:e4b3fb48a503f555ff0a1d33</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H63" s="12" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0063</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 63</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>SHA256:dddb97eb91652f5b642ece93</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0064</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 64</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>SHA256:2e621c2287adb2a3054cea15</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0065</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 65</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>SHA256:7a392e95fbd74f2bd83af1c1</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0066</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 66</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>SHA256:1b50ca93333d4867d6b44d46</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0067</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 67</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>SHA256:19e096cd2d9dae1b4f3aaef7</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0068</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 68</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>SHA256:55c9d6aab4db2b2f22b713f5</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G69" s="12" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0069</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 69</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>SHA256:ee4dfa6cb84a9fd7fc3a2077</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0070</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 70</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>SHA256:648298764a2af70be940f310</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H71" s="12" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0071</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 71</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>SHA256:da11bc3f2e073abfe7ab883c</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="12" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0072</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 72</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>SHA256:520860677a911803b2676921</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H73" s="12" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0073</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 73</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>SHA256:6a2002087c8b2ed5922516f6</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0074</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 74</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>SHA256:d6dcdb3ce633fbbbe4b561b1</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G75" s="12" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0075</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 75</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>SHA256:d915b5e1e680ebc506fcb9e4</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0076</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 76</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>SHA256:54243efb0a4c3445cbd12e5c</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G77" s="12" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H77" s="12" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="12" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0077</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 77</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>SHA256:cf35c2c66616ed0cdb1a2df3</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E78" s="12" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0078</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 78</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>SHA256:48230e437e315f5bfdab0dd4</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G79" s="12" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H79" s="12" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0079</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 79</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>SHA256:51a775a26ce8e3d48f0569aa</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0080</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 80</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>SHA256:9cc13dba8add7bec0e1e63aa</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H81" s="12" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0081</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 81</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>SHA256:fe1f8f5b50b7a6337944ee12</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0082</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 82</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>SHA256:4f0a92b728f52f9055e67914</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G83" s="12" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H83" s="12" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0083</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 83</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>SHA256:1c91a2fbd199c5b8bb40bcaa</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0084</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 84</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>SHA256:6597be44831de74ef2f48c93</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G85" s="12" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H85" s="12" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="12" t="inlineStr">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0085</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 85</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>SHA256:ec81d72c1ee8f9639f1da0c7</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="12" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0086</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 86</t>
         </is>
       </c>
-      <c r="C87" s="12" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>SHA256:f5764ac3a01ae92dc7d800b6</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E87" s="12" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G87" s="12" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H87" s="12" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0087</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 87</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>SHA256:5cc42a632a0701c16babaa14</t>
         </is>
       </c>
-      <c r="D88" s="12" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E88" s="12" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0088</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 88</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>SHA256:085c0ef9db880034d4c8a8aa</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E89" s="12" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G89" s="12" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H89" s="12" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0089</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 89</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>SHA256:ae455e10948a37e8d9ec49bd</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0090</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 90</t>
         </is>
       </c>
-      <c r="C91" s="12" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>SHA256:9e3786c74bbd49edddbc2982</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E91" s="12" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F91" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G91" s="12" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H91" s="12" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0091</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 91</t>
         </is>
       </c>
-      <c r="C92" s="12" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>SHA256:a21857b532115b1c42230399</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E92" s="12" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H92" s="12" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0092</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 92</t>
         </is>
       </c>
-      <c r="C93" s="12" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>SHA256:258788af5762110177df1c71</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E93" s="12" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F93" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G93" s="12" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H93" s="12" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0093</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 93</t>
         </is>
       </c>
-      <c r="C94" s="12" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>SHA256:f18e21487fd6a108663431be</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E94" s="12" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F94" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="inlineStr">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0094</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 94</t>
         </is>
       </c>
-      <c r="C95" s="12" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>SHA256:1162707c9acde069cdd3bdc3</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E95" s="12" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F95" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G95" s="12" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H95" s="12" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="12" t="inlineStr">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0095</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 95</t>
         </is>
       </c>
-      <c r="C96" s="12" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>SHA256:0a568ec5c427b062bb6100f1</t>
         </is>
       </c>
-      <c r="D96" s="12" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E96" s="12" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F96" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H96" s="12" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0096</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 96</t>
         </is>
       </c>
-      <c r="C97" s="12" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>SHA256:baf1aff3f235e6cabe347606</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E97" s="12" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F97" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H97" s="12" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="12" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0097</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 97</t>
         </is>
       </c>
-      <c r="C98" s="12" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>SHA256:23bff035e23288c977168419</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E98" s="12" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F98" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G98" s="12" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H98" s="12" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="12" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0098</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 98</t>
         </is>
       </c>
-      <c r="C99" s="12" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>SHA256:4954aabb066fc0ec6ddcd1fb</t>
         </is>
       </c>
-      <c r="D99" s="12" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E99" s="12" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F99" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G99" s="12" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H99" s="12" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="12" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0099</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 99</t>
         </is>
       </c>
-      <c r="C100" s="12" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>SHA256:418979642d88c8ef8f773d9f</t>
         </is>
       </c>
-      <c r="D100" s="12" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E100" s="12" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F100" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G100" s="12" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H100" s="12" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="12" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0100</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 100</t>
         </is>
       </c>
-      <c r="C101" s="12" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>SHA256:5cc38c8c840947984ff65921</t>
         </is>
       </c>
-      <c r="D101" s="12" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E101" s="12" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F101" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G101" s="12" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H101" s="12" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="12" t="inlineStr">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0101</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 101</t>
         </is>
       </c>
-      <c r="C102" s="12" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>SHA256:e63573f39c8c5de853278444</t>
         </is>
       </c>
-      <c r="D102" s="12" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E102" s="12" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F102" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G102" s="12" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H102" s="12" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0102</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 102</t>
         </is>
       </c>
-      <c r="C103" s="12" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>SHA256:5be6048a7e97fee8eff18339</t>
         </is>
       </c>
-      <c r="D103" s="12" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E103" s="12" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F103" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G103" s="12" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H103" s="12" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="12" t="inlineStr">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0103</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 103</t>
         </is>
       </c>
-      <c r="C104" s="12" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>SHA256:a77af74c3be52e4b035b3b34</t>
         </is>
       </c>
-      <c r="D104" s="12" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E104" s="12" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F104" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G104" s="12" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H104" s="12" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="12" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0104</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 104</t>
         </is>
       </c>
-      <c r="C105" s="12" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>SHA256:e184eb8fc6a75330a13cfffd</t>
         </is>
       </c>
-      <c r="D105" s="12" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E105" s="12" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F105" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G105" s="12" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H105" s="12" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="12" t="inlineStr">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0105</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 105</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>SHA256:659d41aa2a9e1ddfe7aef3bf</t>
         </is>
       </c>
-      <c r="D106" s="12" t="inlineStr">
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E106" s="12" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F106" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G106" s="12" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H106" s="12" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0106</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 106</t>
         </is>
       </c>
-      <c r="C107" s="12" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>SHA256:a63c23969482903391d08f93</t>
         </is>
       </c>
-      <c r="D107" s="12" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E107" s="12" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F107" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G107" s="12" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H107" s="12" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="12" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0107</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 107</t>
         </is>
       </c>
-      <c r="C108" s="12" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>SHA256:3f9a018e33ba0d3c12b9b3cd</t>
         </is>
       </c>
-      <c r="D108" s="12" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E108" s="12" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F108" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G108" s="12" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H108" s="12" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="12" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0108</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 108</t>
         </is>
       </c>
-      <c r="C109" s="12" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>SHA256:f8b643183d4554e185e0ffa0</t>
         </is>
       </c>
-      <c r="D109" s="12" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E109" s="12" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F109" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G109" s="12" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H109" s="12" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="12" t="inlineStr">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0109</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 109</t>
         </is>
       </c>
-      <c r="C110" s="12" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>SHA256:06e1f268c255b106f5140901</t>
         </is>
       </c>
-      <c r="D110" s="12" t="inlineStr">
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E110" s="12" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F110" s="12" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G110" s="12" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H110" s="12" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
         </is>

--- a/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
+++ b/public/chat_files/keegan_sku_margin_calculator_v1.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -87,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,7 +101,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,7 +116,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -478,205 +493,1343 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SKU Code</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Description</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>FOB</t>
+          <t>FOB Ningbo USD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ocean/Unit</t>
+          <t>Ocean Freight / Unit</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Duty/Unit</t>
+          <t>Customs Tariff (24.5%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Landed</t>
+          <t>Port Drayage / Unit</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Total Landed Cost</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Amazon FBA Fee</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Reorder Level</t>
+          <t>FBA Referral (15%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Wholesale Price (50% Margin)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Retail MSRP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KC-101</t>
+          <t>PHG-WD-01</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Precision Kettle</t>
+          <t>Acacia Cutting Board (M)</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>10.37</v>
+        <v>4.25</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.22</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>69.5%</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>180</v>
+        <v>6.09</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>51.3</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>KC-102</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Burr Grinder</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>73.7%</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>120</v>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>PHG-WD-02</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Acacia Cutting Board (L)</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>50.8</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KC-103</t>
+          <t>PHG-WD-03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Digital Scale</t>
+          <t>Teak Butcher Block</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E4" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>PHG-WD-04</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Walnut Serving Platter</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PHG-WD-05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Teak Salad Bowl Set</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CR-01</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic Coffee Mug (12oz)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PHG-CR-02</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Ceramic Tumbler (16oz)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CR-03</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic Dinner Plate (10.5in)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PHG-CR-04</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Ceramic Salad Plate (8.5in)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CR-05</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic Pasta Bowl (9in)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>PHG-GL-01</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Ribbed Rocks Glass (10oz)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>PHG-GL-02</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Ribbed Highball Glass (14oz)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>0.28</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E13" s="11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PHG-GL-03</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Glass Cocktail Decanter</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>PHG-TX-01</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>French Linen Towel (2pk)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PHG-TX-02</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Linen Table Runner</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>PHG-TX-03</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Linen Napkin Set (4pk)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PHG-MT-01</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Brass Measuring Cups Set</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>PHG-MT-02</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Vintage Brass Shaker</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PHG-MT-03</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Japanese Brass Jigger</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>PHG-MT-04</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Cast Iron Skillet (10in)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PHG-MT-05</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cast Iron Skillet (12in)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CD-01</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Soy Candle in Ceramic (8oz)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PHG-CD-02</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Soy Candle in Brass (12oz)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>PHG-CD-03</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Reed Diffuser (200ml)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PHG-ST-01</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Hyacinth Storage Basket (M)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>PHG-ST-02</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Hyacinth Storage Basket (L)</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J27" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>76.9%</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>KC-104</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Glass Mugs 2pk</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="G5" s="7" t="n">
+      <c r="K27" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PHG-BA-01</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Waffle Bath Towel</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>80.6%</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>300</v>
+      <c r="K28" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>PHG-BA-02</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Waffle Hand Towel (2pk)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PHG-BA-03</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Stone Bath Mat</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>PHG-WD-06</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Teak Coaster Set (4pk)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>63.3</v>
       </c>
     </row>
   </sheetData>
@@ -746,4578 +1899,4578 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 1</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>SHA256:540deb7669156511c863dbdb</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0002</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 2</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>SHA256:f7ded495162de72a67ea4854</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0003</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 3</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>SHA256:3603c066f7b4ae9f054e5111</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0004</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 4</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>SHA256:c969b391f9880820a54ce678</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0005</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>SHA256:6e71561121d19b8411a621a1</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0006</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 6</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>SHA256:f7b801a9f3202419f7f4e492</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0007</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 7</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>SHA256:62c62c7a9f43b42884529245</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0008</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 8</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>SHA256:dbc2e9293e6bf2bebbde2d60</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0009</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 9</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>SHA256:30fa42537bfb0437c7d43e37</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0010</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 10</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>SHA256:cc8941aee2b2a57b46d8edae</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0011</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 11</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>SHA256:c4e22e088306f3cd8770f119</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0012</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 12</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>SHA256:f55501bcdbd7fafd92c81471</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0013</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 13</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>SHA256:4cfd0482bc4748af31620541</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0014</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 14</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>SHA256:74e0bb3f9db2a3792faadd00</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0015</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 15</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>SHA256:a2813dfe324b68fdf80130e9</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0016</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 16</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>SHA256:da87bc08a2c815ea4dc1d48a</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0017</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 17</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>SHA256:a8f5da4cf51f88e603619b80</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0018</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 18</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>SHA256:c21d335aaec1b52645d3a0fe</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0019</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 19</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>SHA256:6226f132a709b57fabf39378</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0020</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 20</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>SHA256:f9c362babff802eb5fdcffac</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0021</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 21</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>SHA256:c83f61074c0f6e432b45ece0</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0022</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 22</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>SHA256:3861a893cb80e9590d73222c</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0023</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 23</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>SHA256:fe2ddacde461256b5f08d27c</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0024</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 24</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>SHA256:7906cc548202d1de58a3f737</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0025</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 25</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>SHA256:73c8c85772c3221ccff8c47e</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0026</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 26</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>SHA256:d1317d3978037deb08339516</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0027</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 27</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>SHA256:d43c6575b0ca1b68f50e33d4</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0028</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 28</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>SHA256:8520908b382e44b134e4f0eb</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0029</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 29</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>SHA256:d2566c955ed7f9bc26364e60</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0030</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 30</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>SHA256:b4f0e1378d635abca34eda22</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0031</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 31</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>SHA256:78a118d65b25b93080f3b36f</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0032</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 32</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>SHA256:e64ac7dc72d65d553c4cf25b</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0033</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 33</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>SHA256:738de8a6e48106eb66e6f369</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0034</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 34</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>SHA256:ed2cb0a3fb6e1548cd864f5d</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0035</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 35</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>SHA256:ef0a284ba0d6384307c01481</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0036</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 36</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>SHA256:bf112b05b70f8b03185be9ae</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0037</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 37</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>SHA256:066dfee11d424a9f6652c67c</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0038</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 38</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>SHA256:de55bfd4bc6fcd3f71abf340</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0039</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 39</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>SHA256:4ff7804472b80e24af920ee2</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0040</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 40</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>SHA256:5365440c9322e125b6ce76a8</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0041</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 41</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>SHA256:d86edb3e5abf4a4c69b8d8a9</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0042</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 42</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>SHA256:b45db66614f1c2231f3a7ef9</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0043</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 43</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>SHA256:bc2d8644a130a9886a876877</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0044</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 44</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>SHA256:4fc5f10491b1a050e770c3ba</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0045</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 45</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>SHA256:f9868fe5f8094b7c04ab2ce8</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0046</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 46</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>SHA256:44a389c09415a366c84dbccf</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0047</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 47</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>SHA256:552719fb71cb09b1fc870977</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0048</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 48</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>SHA256:e1f155c4095487c58f71c703</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0049</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 49</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>SHA256:147fc2ced54f682ccca1b558</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0050</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 50</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>SHA256:57cb0c402fb86a86035e226c</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0051</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 51</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>SHA256:8a5605f39e6d4aafc493881b</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H52" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0052</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 52</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>SHA256:69f0f97019e43cead9a93c35</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0053</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 53</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>SHA256:ddea4861aa07f1fd06d7eadb</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0054</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 54</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>SHA256:2022ef4c0c663f4c0a0f82b2</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0055</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 55</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>SHA256:7d07873b0b0884a12d22b25c</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0056</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 56</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>SHA256:bd6871a57c26803de031a923</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0057</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 57</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>SHA256:2948ed50e398f60c5fd03b2d</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0058</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 58</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>SHA256:59d2740a341a8effe4ed00f1</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0059</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 59</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>SHA256:e4d7119b6591198b6b498b0e</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0060</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 60</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>SHA256:074f9f0effc80d638a5a5b64</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H61" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0061</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 61</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
         <is>
           <t>SHA256:3afc4ed9e9183dff8d3bddeb</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0062</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 62</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>SHA256:e4b3fb48a503f555ff0a1d33</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H63" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0063</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 63</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
         <is>
           <t>SHA256:dddb97eb91652f5b642ece93</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0064</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 64</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>SHA256:2e621c2287adb2a3054cea15</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0065</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 65</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr">
         <is>
           <t>SHA256:7a392e95fbd74f2bd83af1c1</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0066</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 66</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr">
         <is>
           <t>SHA256:1b50ca93333d4867d6b44d46</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="H67" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0067</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 67</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>SHA256:19e096cd2d9dae1b4f3aaef7</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="H68" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0068</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 68</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>SHA256:55c9d6aab4db2b2f22b713f5</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="H69" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0069</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 69</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>SHA256:ee4dfa6cb84a9fd7fc3a2077</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H70" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0070</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 70</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
         <is>
           <t>SHA256:648298764a2af70be940f310</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="H71" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0071</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 71</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="12" t="inlineStr">
         <is>
           <t>SHA256:da11bc3f2e073abfe7ab883c</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E72" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="H72" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0072</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 72</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>SHA256:520860677a911803b2676921</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="H73" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0073</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 73</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>SHA256:6a2002087c8b2ed5922516f6</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0074</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 74</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>SHA256:d6dcdb3ce633fbbbe4b561b1</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="H75" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0075</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 75</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" s="12" t="inlineStr">
         <is>
           <t>SHA256:d915b5e1e680ebc506fcb9e4</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0076</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 76</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>SHA256:54243efb0a4c3445cbd12e5c</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="H77" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0077</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 77</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" s="12" t="inlineStr">
         <is>
           <t>SHA256:cf35c2c66616ed0cdb1a2df3</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E78" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0078</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 78</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="12" t="inlineStr">
         <is>
           <t>SHA256:48230e437e315f5bfdab0dd4</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H79" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0079</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 79</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C80" s="12" t="inlineStr">
         <is>
           <t>SHA256:51a775a26ce8e3d48f0569aa</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0080</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 80</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C81" s="12" t="inlineStr">
         <is>
           <t>SHA256:9cc13dba8add7bec0e1e63aa</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="H81" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0081</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 81</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C82" s="12" t="inlineStr">
         <is>
           <t>SHA256:fe1f8f5b50b7a6337944ee12</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H82" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0082</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 82</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C83" s="12" t="inlineStr">
         <is>
           <t>SHA256:4f0a92b728f52f9055e67914</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="H83" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0083</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 83</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C84" s="12" t="inlineStr">
         <is>
           <t>SHA256:1c91a2fbd199c5b8bb40bcaa</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="H84" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0084</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 84</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C85" s="12" t="inlineStr">
         <is>
           <t>SHA256:6597be44831de74ef2f48c93</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D85" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="H85" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0085</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 85</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C86" s="12" t="inlineStr">
         <is>
           <t>SHA256:ec81d72c1ee8f9639f1da0c7</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="H86" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0086</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 86</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C87" s="12" t="inlineStr">
         <is>
           <t>SHA256:f5764ac3a01ae92dc7d800b6</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="H87" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0087</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 87</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C88" s="12" t="inlineStr">
         <is>
           <t>SHA256:5cc42a632a0701c16babaa14</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E88" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="H88" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0088</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 88</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C89" s="12" t="inlineStr">
         <is>
           <t>SHA256:085c0ef9db880034d4c8a8aa</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr">
+      <c r="H89" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0089</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 89</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="12" t="inlineStr">
         <is>
           <t>SHA256:ae455e10948a37e8d9ec49bd</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E90" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="H90" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0090</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 90</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C91" s="12" t="inlineStr">
         <is>
           <t>SHA256:9e3786c74bbd49edddbc2982</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E91" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="H91" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0091</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 91</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C92" s="12" t="inlineStr">
         <is>
           <t>SHA256:a21857b532115b1c42230399</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E92" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="H92" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0092</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 92</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C93" s="12" t="inlineStr">
         <is>
           <t>SHA256:258788af5762110177df1c71</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D93" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E93" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="H93" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0093</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 93</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C94" s="12" t="inlineStr">
         <is>
           <t>SHA256:f18e21487fd6a108663431be</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E94" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0094</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 94</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C95" s="12" t="inlineStr">
         <is>
           <t>SHA256:1162707c9acde069cdd3bdc3</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D95" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H95" s="8" t="inlineStr">
+      <c r="H95" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0095</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 95</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C96" s="12" t="inlineStr">
         <is>
           <t>SHA256:0a568ec5c427b062bb6100f1</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="H96" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0096</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 96</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>SHA256:baf1aff3f235e6cabe347606</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H97" s="8" t="inlineStr">
+      <c r="H97" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0097</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 97</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>SHA256:23bff035e23288c977168419</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D98" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr">
+      <c r="H98" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0098</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 98</t>
         </is>
       </c>
-      <c r="C99" s="8" t="inlineStr">
+      <c r="C99" s="12" t="inlineStr">
         <is>
           <t>SHA256:4954aabb066fc0ec6ddcd1fb</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D99" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr">
+      <c r="H99" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0099</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 99</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C100" s="12" t="inlineStr">
         <is>
           <t>SHA256:418979642d88c8ef8f773d9f</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="D100" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr">
+      <c r="H100" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0100</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 100</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C101" s="12" t="inlineStr">
         <is>
           <t>SHA256:5cc38c8c840947984ff65921</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D101" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E101" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="H101" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0101</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 101</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C102" s="12" t="inlineStr">
         <is>
           <t>SHA256:e63573f39c8c5de853278444</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D102" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr">
+      <c r="H102" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0102</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 102</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C103" s="12" t="inlineStr">
         <is>
           <t>SHA256:5be6048a7e97fee8eff18339</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D103" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
+      <c r="E103" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr">
+      <c r="H103" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0103</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 103</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C104" s="12" t="inlineStr">
         <is>
           <t>SHA256:a77af74c3be52e4b035b3b34</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D104" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
+      <c r="E104" s="12" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr">
+      <c r="H104" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0104</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 104</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C105" s="12" t="inlineStr">
         <is>
           <t>SHA256:e184eb8fc6a75330a13cfffd</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D105" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E105" s="12" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr">
+      <c r="H105" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A106" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0105</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 105</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C106" s="12" t="inlineStr">
         <is>
           <t>SHA256:659d41aa2a9e1ddfe7aef3bf</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D106" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E106" s="12" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G106" s="8" t="inlineStr">
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H106" s="8" t="inlineStr">
+      <c r="H106" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0106</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 106</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C107" s="12" t="inlineStr">
         <is>
           <t>SHA256:a63c23969482903391d08f93</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
+      <c r="E107" s="12" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H107" s="8" t="inlineStr">
+      <c r="H107" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0107</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 107</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" s="12" t="inlineStr">
         <is>
           <t>SHA256:3f9a018e33ba0d3c12b9b3cd</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D108" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E108" s="12" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr">
+      <c r="H108" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="A109" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0108</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 108</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C109" s="12" t="inlineStr">
         <is>
           <t>SHA256:f8b643183d4554e185e0ffa0</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D109" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E109" s="12" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr">
+      <c r="H109" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="A110" s="12" t="inlineStr">
         <is>
           <t>AUD-REC-0109</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 109</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C110" s="12" t="inlineStr">
         <is>
           <t>SHA256:06e1f268c255b106f5140901</t>
         </is>
       </c>
-      <c r="D110" s="8" t="inlineStr">
+      <c r="D110" s="12" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H110" s="8" t="inlineStr">
+      <c r="H110" s="12" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
         </is>
